--- a/data/pack/ca/pienso_cerdo_ab.xlsx
+++ b/data/pack/ca/pienso_cerdo_ab.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1314,6 +1314,61 @@
         </is>
       </c>
       <c r="K16" t="inlineStr">
+        <is>
+          <t>Contains information licensed under the Open Government Licence – Alberta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>pienso_cerdo_ab</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Pienso de crecimiento para cerdos (Alberta)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>719.2</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>tonelada</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Alberta Agriculture and Irrigation — Weekly Market Review</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>OGL-Alberta</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>Contains information licensed under the Open Government Licence – Alberta.</t>
         </is>
@@ -1417,7 +1472,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1483,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -1523,7 +1578,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
